--- a/Arquivos/bases_apoio/tab_de-para.xlsx
+++ b/Arquivos/bases_apoio/tab_de-para.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="entidade" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="entidade" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'status'!$A$1:$B$24</definedName>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -810,6 +810,30 @@
       <c r="B27" t="inlineStr">
         <is>
           <t>Interessado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INFORMAÇÕES POR E-MAIL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Contato c/ Decisor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JÁ INSCRITO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Contato c/ Decisor</t>
         </is>
       </c>
     </row>
